--- a/artfynd/A 21113-2026 artfynd.xlsx
+++ b/artfynd/A 21113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66863393</v>
+        <v>66863392</v>
       </c>
       <c r="B2" t="n">
-        <v>96943</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222302</v>
+        <v>269</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Älvstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Carex rhynchophysa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733637.5652196988</v>
+        <v>733638</v>
       </c>
       <c r="R2" t="n">
-        <v>7099084.349972206</v>
+        <v>7099084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,24 +746,14 @@
           <t>2017-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-07-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Osäker.  Mycket tanig starr med få frukter med tydlig näbb.  Belägg.</t>
+          <t>osäker; storväxt och flaskstarrsliknande, med trekantig och sträv stjälk.  Belägg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66863392</v>
+        <v>67366142</v>
       </c>
       <c r="B3" t="n">
-        <v>97055</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,23 +808,35 @@
           <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>bäckravin mellan E12:an och Tvärån SV om reservatsparkeringen, Starrberget, Vb</t>
+          <t>E12, bäckravin 600m NO om Tömptjärnen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733637.5652196988</v>
+        <v>733675</v>
       </c>
       <c r="R3" t="n">
-        <v>7099084.349972206</v>
+        <v>7099106</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,34 +860,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>osäker; storväxt och flaskstarrsliknande, med trekantig och sträv stjälk.  Belägg.</t>
+          <t>ca 2500 skott/plantor, ca 100 m2 tätt bestånd i vid bäcken, V om E12 - så vitt jag kunde se typisk älvstarr men fruktgömmena mjuka/tomma så kanske med inblandning av flaskstarr ändå?</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -903,27 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67366142</v>
+        <v>104454147</v>
       </c>
       <c r="B4" t="n">
-        <v>97055</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,35 +925,24 @@
           <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>E12, bäckravin 600m NO om Tömptjärnen, Vb</t>
+          <t>Tömptjärnen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733674.8166430967</v>
+        <v>733695</v>
       </c>
       <c r="R4" t="n">
-        <v>7099106.117652422</v>
+        <v>7099091</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,27 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 2500 skott/plantor, ca 100 m2 tätt bestånd i vid bäcken, V om E12 - så vitt jag kunde se typisk älvstarr men fruktgömmena mjuka/tomma så kanske med inblandning av flaskstarr ändå?</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,65 +986,76 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Bård Haugsrud</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Bård Haugsrud, Asle Bruserud</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101940167</v>
+        <v>118151974</v>
       </c>
       <c r="B5" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224364</v>
+        <v>269</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Älvstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Carex rhynchophysa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>S om Starrberget, Vb</t>
+          <t>bäckravin V om E12, S om Starrberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733708.9200682784</v>
+        <v>733666</v>
       </c>
       <c r="R5" t="n">
-        <v>7099075.57843082</v>
+        <v>7099106</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,22 +1079,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>mycket rikligt, belägg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,15 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104454147</v>
+        <v>127926594</v>
       </c>
       <c r="B6" t="n">
-        <v>97055</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,14 +1152,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tömptjärnen, Vb</t>
+          <t>Tömptjärnen, Tömptjärnen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733695.3669137452</v>
+        <v>733686</v>
       </c>
       <c r="R6" t="n">
-        <v>7099091.331001824</v>
+        <v>7099120</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,22 +1186,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,33 +1210,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bård Haugsrud</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bård Haugsrud, Asle Bruserud</t>
+          <t>Filippa Paperin, Elvira Klang, Elis Lewin, Tore Dahlberg, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118151974</v>
+        <v>124948515</v>
       </c>
       <c r="B7" t="n">
-        <v>98598</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,53 +1240,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>269</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Älvstarr</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex rhynchophysa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>bäckravin V om E12, S om Starrberget, Vb</t>
+          <t>Tvärån, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733666</v>
+        <v>733640</v>
       </c>
       <c r="R7" t="n">
-        <v>7099106</v>
+        <v>7099070</v>
       </c>
       <c r="S7" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,17 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>mycket rikligt, belägg</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,27 +1318,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118151984</v>
+        <v>125689155</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,45 +1341,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S om Starrberget, Vb</t>
+          <t>Tömptjärnen, Tömptjärnen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733709</v>
+        <v>733652</v>
       </c>
       <c r="R8" t="n">
         <v>7099076</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1478,12 +1395,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,49 +1425,54 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Magnus Friberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Magnus Friberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124948182</v>
+        <v>124947948</v>
       </c>
       <c r="B9" t="n">
-        <v>91184</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1548,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733661</v>
+        <v>733698</v>
       </c>
       <c r="R9" t="n">
-        <v>7099128</v>
+        <v>7098787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,18 +1518,12 @@
           <t>2025-05-10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ymnigt växande på på högstubbe och tillhörande låga</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1619,11 +1545,11 @@
         <v>124948300</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1726,37 +1652,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124948332</v>
+        <v>124948324</v>
       </c>
       <c r="B11" t="n">
-        <v>91184</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1764,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>733602</v>
+        <v>733614</v>
       </c>
       <c r="R11" t="n">
-        <v>7099269</v>
+        <v>7099281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,7 +1739,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1827,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124948324</v>
+        <v>118151984</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,16 +1768,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1866,17 +1796,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tvärån, Vb</t>
+          <t>S om Starrberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733614</v>
+        <v>733709</v>
       </c>
       <c r="R12" t="n">
-        <v>7099281</v>
+        <v>7099076</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,12 +1830,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1850,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124947948</v>
+        <v>124948146</v>
       </c>
       <c r="B13" t="n">
-        <v>57632</v>
+        <v>57369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,29 +1873,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>102961</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1975,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733698</v>
+        <v>733527</v>
       </c>
       <c r="R13" t="n">
-        <v>7098787</v>
+        <v>7099037</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124948533</v>
+        <v>124990320</v>
       </c>
       <c r="B14" t="n">
-        <v>56226</v>
+        <v>57369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,16 +1982,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>102961</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2065,12 +1999,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2080,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733592</v>
+        <v>733512</v>
       </c>
       <c r="R14" t="n">
-        <v>7099120</v>
+        <v>7099085</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,12 +2048,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,7 +2083,7 @@
         <v>124948124</v>
       </c>
       <c r="B15" t="n">
-        <v>58001</v>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124948515</v>
+        <v>124948533</v>
       </c>
       <c r="B16" t="n">
-        <v>82737</v>
+        <v>56522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,26 +2200,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>206004</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733640</v>
+        <v>733592</v>
       </c>
       <c r="R16" t="n">
-        <v>7099070</v>
+        <v>7099120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2276,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2352,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125689155</v>
+        <v>66863404</v>
       </c>
       <c r="B17" t="n">
-        <v>82789</v>
+        <v>102464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,34 +2305,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>221343</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tömptjärnen, Tömptjärnen, Vb</t>
+          <t>E12:an: vägdike S om reservatsparkeringen, Starrberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733652</v>
+        <v>733696</v>
       </c>
       <c r="R17" t="n">
-        <v>7099076</v>
+        <v>7099195</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,22 +2359,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2017-07-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,61 +2384,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Friberg</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Friberg</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127926594</v>
+        <v>66863393</v>
       </c>
       <c r="B18" t="n">
-        <v>99341</v>
+        <v>99771</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>269</v>
+        <v>222302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Älvstarr</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carex rhynchophysa</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tömptjärnen, Tömptjärnen, Vb</t>
+          <t>bäckravin mellan E12:an och Tvärån SV om reservatsparkeringen, Starrberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733686</v>
+        <v>733638</v>
       </c>
       <c r="R18" t="n">
-        <v>7099120</v>
+        <v>7099084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2528,46 +2464,138 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2017-07-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Osäker.  Mycket tanig starr med få frukter med tydlig näbb.  Belägg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elvira Klang, Elis Lewin, Tore Dahlberg, Karl Soler Kinnerbäck</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>101940167</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>S om Starrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>733709</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7099076</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21113-2026 artfynd.xlsx
+++ b/artfynd/A 21113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66863392</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67366142</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104454147</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118151974</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127926594</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124948515</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125689155</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124947948</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124948300</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124948324</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118151984</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124948146</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124990320</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2186,6 +2256,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124948124</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124948533</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,6 +2473,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66863404</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2498,6 +2583,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66863393</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2596,8 +2686,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101940167</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>